--- a/requirements_output1.xlsx
+++ b/requirements_output1.xlsx
@@ -79,18 +79,29 @@
   </si>
   <si>
     <t>The STC Program shall determine A_DMC_9 LADC Monitor Status according to the following logic:
-IF (A_DMC_9_LADC_LABELS_VALID == FALSE) THEN
-    A_DMC_9_LADC_Monitor_Status = TRUE
-ELSE IF ((A_DMC_9_LADC_PARITY_OK == TRUE) AND (A_DMC_9_LADC_SSM == "Normal Operation") AND (A_DMC_9_LADC_Airspeed &lt; 35)) THEN
-    A_DMC_9_LADC_Monitor_Status = FALSE
-ELSE
-    No action (A_DMC_9_LADC_Monitor_Status remains unchanged)
-END IF
-Where:
-- A_DMC_9_LADC_LABELS_VALID indicates valid labels received (TRUE/FALSE).
-- A_DMC_9_LADC_PARITY_OK indicates parity correctness (TRUE/FALSE).
-- A_DMC_9_LADC_SSM is the received SSM string value.
-- A_DMC_9_LADC_Airspeed is the received airspeed in knots.</t>
+	IF the following condition is true for 220ms with a tolerance of +10ms
+	    (( No valid A_DMC_9 LADC labels have been received ) OR
+	    (A_DMC_9 LADC data have wrong (even) parity bit) OR
+	    (A_DMC_9 LADC have SSM data set to "Normal Operation")) 
+	THEN
+	     A_DMC_9 LADC Monitor Status = TRUE
+              ELSE
+	     IF  the following condition is true for 320ms with a tolerance of +10ms
+	    ((A_DMC_9 LADC labels have been received at expected update rate with a tolerance of +10ms ) AND
+	    (A_DMC_9 LADC data have correct (odd) parity bit) AND
+	    (A_DMC_9 LADC have SSM data set to "Normal Operation") AND 
+	    (A_DMC_9 LADC Airspeed &lt; 35kts))
+	     THEN
+	          A_DMC_9 LADC Monitor Status = FALSE
+	     ELSE
+	          No action (A_DMC_9 LADC Monitor Status remains unchanged)
+	     ENDIF
+	ENDIF
+Where A_DMC_9 LADC ARINC Message is defined in SCU_STC_SRS_135
+Justification for timing tolerance: ARINC label reception requires tolerance for label polling and processing.
+Object Type:  Traceable
+Reqt Source:  SES
+Verification Method:</t>
   </si>
   <si>
     <t>The STC Program shall convert the Pilot_SHDL_Operation into a steering angle demand Unlimited_Pilot_SHDL_Command  in every Major cycle using the following logic:
@@ -126,25 +137,30 @@
        Unlimited_Pilot_SHDL_Command = (11.6 * Pilot_SHDL_Operation + 110.12deg ) * (1/10.3)
 ELSE IF( Pilot_SHDL_Operation &gt;= -44.3deg )
 THEN
-       Unlimited_Pilot_SHDL_Command = (14.4 * Pilot_SHDL_Operation + 205.32deg ) * (1/10)
+       Unlimited_Pilot_SHDL_Command = (14.4 * Pilot_SHDL_Operation + 205.32deg ) * (1/0)
 ELSE IF( Pilot_SHDL_Operation &gt;= -54.7deg )
 THEN
        Unlimited_Pilot_SHDL_Command = (16.6 * Pilot_SHDL_Operation + 298.58deg ) * (1/10.4)
 END IF
 Where Pilot_SHDL_Operation is the value calculated in SCU_STC_SRS_68
 and Major cycle is defined in Table 6.2-1
-Object :  Traceable
-Reqt Source:  SES</t>
-  </si>
-  <si>
-    <t>The STC Program shall debounce the NLG_WOW1 signal using the following algorithm to generate a filtered version of the signal:
-IF (NLG_WOW1 == TRUE) THEN
-    Debounced_NLG_WOW1 = FALSE
-ELSE IF (NLG_WOW1 == FALSE) THEN
-    Debounced_NLG_WOW1 = TRUE
+Object Type:  Traceable
+Reqt Source:  SES
+Verification Method:</t>
+  </si>
+  <si>
+    <t>The STC Program shall debounce the NLG_WOW1 signal using the following algorithm to generate a filtered version of the signal 
+IF (NLG_WOW1 has been TRUE for the last 1.5s) THEN
+Debounced_NLG_WOW1 = FALSE
+ELSE IF (NLG_WOW1 has been FALSE for the last 100ms) THEN
+Debounced_NLG_WOW1 = TRUE
 ELSE
-    Debounced_NLG_WOW1 remains unchanged, with an initial value of FALSE
-END IF</t>
+Debounced_NLG_WOW1 remains unchanged, with an initial value of FALSE
+ENDIF
+Where NLG_WOW1 is the value calculated in SCU_STC_SRS_139
+Object Type:  Traceable
+Reqt Source:  SES
+Verification Method:</t>
   </si>
   <si>
     <t>The STC Program shall poll the ARINC receivers for the labels listed in the following table more frequently than the transmission frequency:
@@ -167,30 +183,33 @@
 Verification Method:</t>
   </si>
   <si>
-    <t>The CSU shall implement a user input handling loop as follows:
-The CSU shall prompt the user for a string input user_input.
-The CSU shall repeatedly perform the following while user_input matches the termination condition defined in Section 3:
-The CSU shall print the exact string:
-I am In
-The CSU shall prompt the user again for user_input.
-When user_input does not match the termination condition, the CSU shall print the exact string:
-I am out.
-The CSU shall then terminate the loop.</t>
+    <t>The CSU shall implement the following logic:
+BEGIN
+    WHILE TRUE DO
+        INPUT user_input
+        IF user_input = "exit" THEN
+            PRINT "Loop ended."
+            BREAK
+        ELSE
+            PRINT "Still looping..."
+        END IF
+    END WHILE
+END</t>
   </si>
   <si>
     <t>The CSU shall implement the logic below:
 BEGIN
     SET array = [10, 20, 30, 40]
     SET index = INPUT("Enter index:")
-    FOR i=0 to 3 THEN
-           PRINT index
+    FOR i=0 to 4 THEN
+           PRINT "Value at index = ", array[index]
     END LOOP</t>
   </si>
   <si>
     <t>The CSU shall prints the pointer value using below pseudocode:
 BEGIN
     DECLARE variable = 42
-    DECLARE pointer = 32  
+    DECLARE pointer = 32
     pointer = ADDRESS OF variable
 	PRINT "Value at pointer = ", VALUE AT(pointer)
 END</t>
@@ -624,7 +643,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -656,7 +675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -693,17 +712,25 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -714,7 +741,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -772,17 +799,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
